--- a/Tags.xlsx
+++ b/Tags.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/cby5187_psu_edu/Documents/ds 440/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nitiy\lost_and_found\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{790B7349-B52D-45F7-9787-068391FD5384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A593DF74-8F25-4747-90A2-E1FF3262F508}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96FF106-2228-4B09-A0E2-A6DB4BEDC338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="324" yWindow="2688" windowWidth="22716" windowHeight="9960" xr2:uid="{66CB52C6-5648-417D-A949-FA1FBB3F916E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{66CB52C6-5648-417D-A949-FA1FBB3F916E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,135 +41,246 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="104">
   <si>
+    <t>Subway Location</t>
+  </si>
+  <si>
     <t>Color</t>
   </si>
   <si>
+    <t>Item Category</t>
+  </si>
+  <si>
     <t>Item Type</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Bags &amp; Containers</t>
+  </si>
+  <si>
+    <t>Backpack</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Handbag / Purse / Makeup Bag</t>
+  </si>
+  <si>
+    <t>Tote Bag</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Duffel Bag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S </t>
+  </si>
+  <si>
+    <t>Briefcase / Laptop Bag</t>
+  </si>
+  <si>
+    <t>Times Square</t>
+  </si>
+  <si>
+    <t>Wallet</t>
+  </si>
+  <si>
+    <t>Fulton St</t>
+  </si>
+  <si>
+    <t>Fanny Pack / Waist Bag</t>
+  </si>
+  <si>
+    <t>103 St</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Phone / Cell Phone</t>
+  </si>
+  <si>
+    <t>116 St</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>125 St</t>
+  </si>
+  <si>
+    <t>Tablet / iPad</t>
+  </si>
+  <si>
+    <t>57 St</t>
+  </si>
+  <si>
+    <t>Headphones / Earbuds</t>
+  </si>
+  <si>
+    <t>Columbus Circle</t>
+  </si>
+  <si>
+    <t>Smartwatch</t>
+  </si>
+  <si>
+    <t>7 Av</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>72 St</t>
+  </si>
+  <si>
+    <t>Clothing &amp; Apparel</t>
+  </si>
+  <si>
+    <t>Jacket / Coat</t>
+  </si>
+  <si>
+    <t>Franklin Av</t>
+  </si>
+  <si>
+    <t>Sweater / Hoodie</t>
+  </si>
+  <si>
+    <t>Myrtle Av</t>
+  </si>
+  <si>
+    <t>Shirt</t>
+  </si>
+  <si>
+    <t>Prospect Av</t>
+  </si>
+  <si>
+    <t>Pants</t>
+  </si>
+  <si>
+    <t>Shoes</t>
+  </si>
+  <si>
+    <t>Hat</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>Black</t>
   </si>
   <si>
+    <t>Uniform</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>White</t>
   </si>
   <si>
+    <t>Personal Items &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Keys / Keychain</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>Gray</t>
   </si>
   <si>
+    <t>Glasses</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>Red</t>
   </si>
   <si>
+    <t>Watch</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
     <t>Blue</t>
   </si>
   <si>
+    <t>Jewelry</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>Green</t>
   </si>
   <si>
+    <t>Umbrella</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>Yellow</t>
   </si>
   <si>
+    <t>Water Bottle</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>Orange</t>
   </si>
   <si>
+    <t>Book / Notebook / Planner</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>Purple</t>
   </si>
   <si>
+    <t>Identification &amp; Documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID Card / Badge </t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
     <t>Pink</t>
   </si>
   <si>
+    <t>Passport</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
     <t>Brown</t>
   </si>
   <si>
-    <t>Item Category</t>
-  </si>
-  <si>
-    <t>Bags &amp; Containers</t>
-  </si>
-  <si>
-    <t>Backpack</t>
-  </si>
-  <si>
-    <t>Tote Bag</t>
-  </si>
-  <si>
-    <t>Duffel Bag</t>
-  </si>
-  <si>
-    <t>Wallet</t>
-  </si>
-  <si>
-    <t>Fanny Pack / Waist Bag</t>
-  </si>
-  <si>
-    <t>Electronics</t>
-  </si>
-  <si>
-    <t>Phone / Cell Phone</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Tablet / iPad</t>
-  </si>
-  <si>
-    <t>Headphones / Earbuds</t>
-  </si>
-  <si>
-    <t>Smartwatch</t>
-  </si>
-  <si>
-    <t>Camera</t>
-  </si>
-  <si>
-    <t>Clothing &amp; Apparel</t>
-  </si>
-  <si>
-    <t>Jacket / Coat</t>
-  </si>
-  <si>
-    <t>Sweater / Hoodie</t>
-  </si>
-  <si>
-    <t>Shirt</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
-    <t>Personal Items &amp; Accessories</t>
-  </si>
-  <si>
-    <t>Keys / Keychain</t>
-  </si>
-  <si>
-    <t>Watch</t>
-  </si>
-  <si>
-    <t>Jewelry</t>
-  </si>
-  <si>
-    <t>Umbrella</t>
-  </si>
-  <si>
-    <t>Water Bottle</t>
-  </si>
-  <si>
-    <t>Book / Notebook / Planner</t>
-  </si>
-  <si>
-    <t>Identification &amp; Documents</t>
-  </si>
-  <si>
-    <t>Passport</t>
-  </si>
-  <si>
     <t>Credit / Debit Card</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>Mail / Package</t>
   </si>
   <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>Other / Miscellaneous</t>
   </si>
   <si>
@@ -179,70 +290,16 @@
     <t>Instrument Case</t>
   </si>
   <si>
+    <t>Sports Equipment (ex. Ball, Racket)</t>
+  </si>
+  <si>
     <t>Food Container / Lunch Box</t>
   </si>
   <si>
     <t>Other (Unspecified)</t>
   </si>
   <si>
-    <t>Sports Equipment (ex. Ball, Racket)</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S </t>
-  </si>
-  <si>
-    <t>Subway Location</t>
-  </si>
-  <si>
-    <t>Times Square</t>
+    <t>14 St - Union Square</t>
   </si>
   <si>
     <t>Penn Station</t>
@@ -269,21 +326,6 @@
     <t>Washington Square</t>
   </si>
   <si>
-    <t>Fulton St</t>
-  </si>
-  <si>
-    <t>103 St</t>
-  </si>
-  <si>
-    <t>116 St</t>
-  </si>
-  <si>
-    <t>125 St</t>
-  </si>
-  <si>
-    <t>14 St - Union Square</t>
-  </si>
-  <si>
     <t>145 St</t>
   </si>
   <si>
@@ -296,18 +338,6 @@
     <t>Rockefeller</t>
   </si>
   <si>
-    <t>57 St</t>
-  </si>
-  <si>
-    <t>Columbus Circle</t>
-  </si>
-  <si>
-    <t>72 St</t>
-  </si>
-  <si>
-    <t>7 Av</t>
-  </si>
-  <si>
     <t>86 St</t>
   </si>
   <si>
@@ -321,36 +351,6 @@
   </si>
   <si>
     <t>Delancy St</t>
-  </si>
-  <si>
-    <t>Franklin Av</t>
-  </si>
-  <si>
-    <t>Myrtle Av</t>
-  </si>
-  <si>
-    <t>Prospect Av</t>
-  </si>
-  <si>
-    <t>Briefcase / Laptop Bag</t>
-  </si>
-  <si>
-    <t>Shoes</t>
-  </si>
-  <si>
-    <t>Pants</t>
-  </si>
-  <si>
-    <t>Hat</t>
-  </si>
-  <si>
-    <t>Glasses</t>
-  </si>
-  <si>
-    <t>Handbag / Purse / Makeup Bag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID Card / Badge </t>
   </si>
 </sst>
 </file>
@@ -731,122 +731,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DFDEA5-8275-4BDD-BD1D-A1523CB36440}">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
       </c>
       <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
         <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -854,282 +881,261 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>103</v>
+      </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
         <v>51</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1137,10 +1143,10 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1148,10 +1154,10 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1159,10 +1165,10 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1170,10 +1176,10 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1188,92 +1194,82 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
